--- a/output/Test_Cases_collection/TC08 - Checkout with Empty Last Name.xlsx
+++ b/output/Test_Cases_collection/TC08 - Checkout with Empty Last Name.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="44">
   <si>
     <t>Test Case Name</t>
   </si>
@@ -64,6 +64,15 @@
     <t>7</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>Launch the application and open [https://www.saucedemo.com/]</t>
   </si>
   <si>
@@ -79,37 +88,55 @@
     <t>Click on "add-to-cart-sauce-labs-backpack"</t>
   </si>
   <si>
+    <t>Click on "1"</t>
+  </si>
+  <si>
     <t>Click on "checkout"</t>
   </si>
   <si>
     <t>Enter "test" in the "firstName" field</t>
   </si>
   <si>
-    <t>Leave the "lastName" field empty and click "continue"</t>
-  </si>
-  <si>
-    <t>The login page is displayed.</t>
-  </si>
-  <si>
-    <t>Username is entered successfully.</t>
-  </si>
-  <si>
-    <t>Password is entered successfully.</t>
-  </si>
-  <si>
-    <t>User is redirected to [https://www.saucedemo.com/inventory.html].</t>
-  </si>
-  <si>
-    <t>Item is added to the cart.</t>
-  </si>
-  <si>
-    <t>User is redirected to [https://www.saucedemo.com/checkout-step-one.html].</t>
-  </si>
-  <si>
-    <t>First name is entered successfully.</t>
-  </si>
-  <si>
-    <t>Validation error message is displayed: "Error: Last Name is required".</t>
+    <t>Leave "lastName" field empty</t>
+  </si>
+  <si>
+    <t>Enter "76565" in the "postalCode" field</t>
+  </si>
+  <si>
+    <t>Click on "continue"</t>
+  </si>
+  <si>
+    <t>The application login page is displayed.</t>
+  </si>
+  <si>
+    <t>The username is entered successfully.</t>
+  </si>
+  <si>
+    <t>The password is entered successfully.</t>
+  </si>
+  <si>
+    <t>The user is redirected to the inventory page.</t>
+  </si>
+  <si>
+    <t>The item is added to the cart.</t>
+  </si>
+  <si>
+    <t>The cart page is displayed with the selected item.</t>
+  </si>
+  <si>
+    <t>The checkout information page is displayed.</t>
+  </si>
+  <si>
+    <t>The first name is entered successfully.</t>
+  </si>
+  <si>
+    <t>The last name field is left empty.</t>
+  </si>
+  <si>
+    <t>The postal code is entered successfully.</t>
+  </si>
+  <si>
+    <t>An error message is displayed: "Error: Last Name is required".</t>
   </si>
   <si>
     <t>New</t>
@@ -476,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -510,19 +537,19 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -533,16 +560,16 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -553,16 +580,16 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -573,16 +600,16 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -593,16 +620,16 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -613,16 +640,16 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -633,16 +660,16 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -653,16 +680,76 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
